--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/0.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/0.xlsx
@@ -426,13 +426,13 @@
         <v>-12.65012514851686</v>
       </c>
       <c r="E2">
-        <v>-12.5143630128465</v>
+        <v>-18.32905043596746</v>
       </c>
       <c r="F2">
-        <v>-4.049344142150652</v>
+        <v>-3.843443483776001</v>
       </c>
       <c r="G2">
-        <v>-6.545661845251347</v>
+        <v>-9.836736913039076</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.02402090596946</v>
       </c>
       <c r="E3">
-        <v>-12.88552579946318</v>
+        <v>-17.96408260179327</v>
       </c>
       <c r="F3">
-        <v>-4.143088824390666</v>
+        <v>-4.449821676503683</v>
       </c>
       <c r="G3">
-        <v>-6.764604635026855</v>
+        <v>-8.865124553407222</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.46645650585958</v>
       </c>
       <c r="E4">
-        <v>-13.84229725932977</v>
+        <v>-18.86787544424412</v>
       </c>
       <c r="F4">
-        <v>-3.919596955850165</v>
+        <v>-4.003981086438545</v>
       </c>
       <c r="G4">
-        <v>-6.352932734514243</v>
+        <v>-8.810341278250734</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.04512915489729</v>
       </c>
       <c r="E5">
-        <v>-14.36166341479547</v>
+        <v>-19.85155056819028</v>
       </c>
       <c r="F5">
-        <v>-4.318338232126929</v>
+        <v>-4.38019573956358</v>
       </c>
       <c r="G5">
-        <v>-6.415886251353749</v>
+        <v>-9.020933359157455</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.73839025567799</v>
       </c>
       <c r="E6">
-        <v>-16.03596705270342</v>
+        <v>-19.46632234130578</v>
       </c>
       <c r="F6">
-        <v>-4.004362135443833</v>
+        <v>-4.351433166603575</v>
       </c>
       <c r="G6">
-        <v>-6.562497793072858</v>
+        <v>-9.692002230051969</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.549714283732</v>
       </c>
       <c r="E7">
-        <v>-16.04962493031055</v>
+        <v>-21.22117394638816</v>
       </c>
       <c r="F7">
-        <v>-3.960777584545537</v>
+        <v>-4.400116318866102</v>
       </c>
       <c r="G7">
-        <v>-5.793205554796366</v>
+        <v>-8.898510982774573</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.45808187198195</v>
       </c>
       <c r="E8">
-        <v>-16.37002805177525</v>
+        <v>-20.00433222426106</v>
       </c>
       <c r="F8">
-        <v>-3.905913983090723</v>
+        <v>-3.993841041060876</v>
       </c>
       <c r="G8">
-        <v>-6.50634952974764</v>
+        <v>-9.259947381212086</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.45536868049768</v>
       </c>
       <c r="E9">
-        <v>-16.66103231998216</v>
+        <v>-22.22539475690711</v>
       </c>
       <c r="F9">
-        <v>-3.717236739755079</v>
+        <v>-3.933651865573464</v>
       </c>
       <c r="G9">
-        <v>-6.349339796906651</v>
+        <v>-9.150626922516066</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.51325976616067</v>
       </c>
       <c r="E10">
-        <v>-17.52204014000854</v>
+        <v>-21.82317569554583</v>
       </c>
       <c r="F10">
-        <v>-3.421444964298237</v>
+        <v>-3.604317008875062</v>
       </c>
       <c r="G10">
-        <v>-5.95721413322365</v>
+        <v>-9.509795996856004</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.61521571357095</v>
       </c>
       <c r="E11">
-        <v>-17.06241361365202</v>
+        <v>-21.97093980241611</v>
       </c>
       <c r="F11">
-        <v>-3.754946509032721</v>
+        <v>-3.689406080123224</v>
       </c>
       <c r="G11">
-        <v>-6.025607915408717</v>
+        <v>-8.528661532258642</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.7341666010039</v>
       </c>
       <c r="E12">
-        <v>-18.54086075072822</v>
+        <v>-23.6284382732816</v>
       </c>
       <c r="F12">
-        <v>-3.062297164773081</v>
+        <v>-3.087209486044873</v>
       </c>
       <c r="G12">
-        <v>-6.249032853834426</v>
+        <v>-8.805632725312931</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.84591819121905</v>
       </c>
       <c r="E13">
-        <v>-18.72863392545628</v>
+        <v>-23.37323612057933</v>
       </c>
       <c r="F13">
-        <v>-3.271137699060267</v>
+        <v>-3.36662775141798</v>
       </c>
       <c r="G13">
-        <v>-5.448854477018881</v>
+        <v>-9.336334219115958</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.93336971249638</v>
       </c>
       <c r="E14">
-        <v>-19.18982730381945</v>
+        <v>-24.21369825403291</v>
       </c>
       <c r="F14">
-        <v>-3.220580779732608</v>
+        <v>-3.151913263877542</v>
       </c>
       <c r="G14">
-        <v>-5.661730288130975</v>
+        <v>-8.297571660270069</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.97617091825682</v>
       </c>
       <c r="E15">
-        <v>-20.06120080084938</v>
+        <v>-23.9701569219004</v>
       </c>
       <c r="F15">
-        <v>-3.139705613462486</v>
+        <v>-3.444940777311242</v>
       </c>
       <c r="G15">
-        <v>-5.09992937638753</v>
+        <v>-8.414895018349576</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.96920014504216</v>
       </c>
       <c r="E16">
-        <v>-20.22818375140822</v>
+        <v>-25.1930260429317</v>
       </c>
       <c r="F16">
-        <v>-2.861359255508602</v>
+        <v>-2.995877009681811</v>
       </c>
       <c r="G16">
-        <v>-5.043164243409136</v>
+        <v>-8.516832728536844</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.90534621726502</v>
       </c>
       <c r="E17">
-        <v>-21.11772548615693</v>
+        <v>-24.59464254450616</v>
       </c>
       <c r="F17">
-        <v>-2.772747966063736</v>
+        <v>-1.997002602527069</v>
       </c>
       <c r="G17">
-        <v>-4.4120573698871</v>
+        <v>-7.828281509173609</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.79385426826094</v>
       </c>
       <c r="E18">
-        <v>-22.45061841167859</v>
+        <v>-26.32677479549205</v>
       </c>
       <c r="F18">
-        <v>-2.613853015960943</v>
+        <v>-2.767015663636363</v>
       </c>
       <c r="G18">
-        <v>-3.81481926530165</v>
+        <v>-6.704909371195877</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.64395098543179</v>
       </c>
       <c r="E19">
-        <v>-23.08878002578752</v>
+        <v>-25.79798035714238</v>
       </c>
       <c r="F19">
-        <v>-2.547471794137605</v>
+        <v>-2.473287351379895</v>
       </c>
       <c r="G19">
-        <v>-3.761387853427653</v>
+        <v>-7.895536707477547</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.47192941001183</v>
       </c>
       <c r="E20">
-        <v>-23.72740354424522</v>
+        <v>-27.02608892260056</v>
       </c>
       <c r="F20">
-        <v>-2.139213404770077</v>
+        <v>-1.875259102072431</v>
       </c>
       <c r="G20">
-        <v>-3.166348167287032</v>
+        <v>-6.862896908061582</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.3001067495244</v>
       </c>
       <c r="E21">
-        <v>-24.05128906222182</v>
+        <v>-29.82910112149832</v>
       </c>
       <c r="F21">
-        <v>-1.747057649345569</v>
+        <v>-1.820904946570339</v>
       </c>
       <c r="G21">
-        <v>-3.523115387445455</v>
+        <v>-6.989824401645581</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.14368844026816</v>
       </c>
       <c r="E22">
-        <v>-25.05594913471952</v>
+        <v>-28.75930347887429</v>
       </c>
       <c r="F22">
-        <v>-1.551828019853781</v>
+        <v>-1.710586289335112</v>
       </c>
       <c r="G22">
-        <v>-3.7033167942686</v>
+        <v>-6.386955720864125</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.02185573696172</v>
       </c>
       <c r="E23">
-        <v>-25.65427376298297</v>
+        <v>-29.91447191349092</v>
       </c>
       <c r="F23">
-        <v>-1.40217433649662</v>
+        <v>-1.082726873118032</v>
       </c>
       <c r="G23">
-        <v>-3.112313010646096</v>
+        <v>-6.44330413870447</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.938286671971229</v>
       </c>
       <c r="E24">
-        <v>-26.13559167983623</v>
+        <v>-29.84766786492976</v>
       </c>
       <c r="F24">
-        <v>-1.230285615313514</v>
+        <v>-1.0923930923413</v>
       </c>
       <c r="G24">
-        <v>-3.291890985372946</v>
+        <v>-6.418160137894445</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.896406207774579</v>
       </c>
       <c r="E25">
-        <v>-27.08955548581806</v>
+        <v>-30.12246019618921</v>
       </c>
       <c r="F25">
-        <v>-0.9222265469886142</v>
+        <v>-1.201788119922405</v>
       </c>
       <c r="G25">
-        <v>-3.421230176803138</v>
+        <v>-7.143687443011062</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.887448766840258</v>
       </c>
       <c r="E26">
-        <v>-26.47025496595108</v>
+        <v>-30.39548642258566</v>
       </c>
       <c r="F26">
-        <v>-1.240576423558492</v>
+        <v>-1.076756000878653</v>
       </c>
       <c r="G26">
-        <v>-3.34339303896999</v>
+        <v>-5.613335551350725</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.895064414376522</v>
       </c>
       <c r="E27">
-        <v>-26.54415513328225</v>
+        <v>-30.38153419416803</v>
       </c>
       <c r="F27">
-        <v>-0.8492921106417288</v>
+        <v>-1.145150155490795</v>
       </c>
       <c r="G27">
-        <v>-4.026884614688562</v>
+        <v>-6.803792264111303</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.904600960884368</v>
       </c>
       <c r="E28">
-        <v>-26.4946498554304</v>
+        <v>-31.1705098423914</v>
       </c>
       <c r="F28">
-        <v>-0.7540969570794125</v>
+        <v>-0.6109583833452691</v>
       </c>
       <c r="G28">
-        <v>-3.508740355793528</v>
+        <v>-5.870228949682772</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.890315473278731</v>
       </c>
       <c r="E29">
-        <v>-27.0613612066463</v>
+        <v>-30.39456034965109</v>
       </c>
       <c r="F29">
-        <v>-0.9155822120507593</v>
+        <v>-1.289080648462014</v>
       </c>
       <c r="G29">
-        <v>-4.033135341759304</v>
+        <v>-6.361053757873869</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.836905884496478</v>
       </c>
       <c r="E30">
-        <v>-26.22037829868184</v>
+        <v>-30.60691181705577</v>
       </c>
       <c r="F30">
-        <v>-0.9044854023228571</v>
+        <v>-1.249078786580826</v>
       </c>
       <c r="G30">
-        <v>-4.635091842947235</v>
+        <v>-6.299662102496658</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.725585057718982</v>
       </c>
       <c r="E31">
-        <v>-26.88121398214717</v>
+        <v>-30.20533353476658</v>
       </c>
       <c r="F31">
-        <v>-1.173129092887751</v>
+        <v>-1.201858531151643</v>
       </c>
       <c r="G31">
-        <v>-4.397416559288857</v>
+        <v>-6.712721959728915</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.547133514204198</v>
       </c>
       <c r="E32">
-        <v>-26.81285666700138</v>
+        <v>-30.35317009722099</v>
       </c>
       <c r="F32">
-        <v>-1.009640017169032</v>
+        <v>-1.430574912901601</v>
       </c>
       <c r="G32">
-        <v>-4.764811656078322</v>
+        <v>-8.094700293692721</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.298901476083204</v>
       </c>
       <c r="E33">
-        <v>-26.74843006729425</v>
+        <v>-30.85704887158046</v>
       </c>
       <c r="F33">
-        <v>-1.198059638242405</v>
+        <v>-1.254149223453362</v>
       </c>
       <c r="G33">
-        <v>-4.604825855282916</v>
+        <v>-7.234344313476961</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.97937198708113</v>
       </c>
       <c r="E34">
-        <v>-25.03040401284225</v>
+        <v>-29.1536928086763</v>
       </c>
       <c r="F34">
-        <v>-1.121143239790262</v>
+        <v>-1.243381275584371</v>
       </c>
       <c r="G34">
-        <v>-4.887450593084128</v>
+        <v>-7.458340184454014</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.601422125608067</v>
       </c>
       <c r="E35">
-        <v>-25.58721611987739</v>
+        <v>-29.86918943765122</v>
       </c>
       <c r="F35">
-        <v>-1.087658144266898</v>
+        <v>-1.931306440545846</v>
       </c>
       <c r="G35">
-        <v>-4.87609100404533</v>
+        <v>-8.040665137051786</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.172472519579021</v>
       </c>
       <c r="E36">
-        <v>-25.08758958261111</v>
+        <v>-29.37587332891464</v>
       </c>
       <c r="F36">
-        <v>-1.267079210243659</v>
+        <v>-1.455163342518899</v>
       </c>
       <c r="G36">
-        <v>-4.609908467478497</v>
+        <v>-6.603581968218665</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.711047559363655</v>
       </c>
       <c r="E37">
-        <v>-24.96225953597483</v>
+        <v>-30.07537538769446</v>
       </c>
       <c r="F37">
-        <v>-1.659242420974793</v>
+        <v>-1.695586212405219</v>
       </c>
       <c r="G37">
-        <v>-4.461495535123253</v>
+        <v>-5.919562115829023</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.23176201793558</v>
       </c>
       <c r="E38">
-        <v>-24.68977219798529</v>
+        <v>-29.30495742595452</v>
       </c>
       <c r="F38">
-        <v>-1.433224860223156</v>
+        <v>-1.797148197825452</v>
       </c>
       <c r="G38">
-        <v>-4.49259167184211</v>
+        <v>-7.324187440996116</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.750790332905113</v>
       </c>
       <c r="E39">
-        <v>-23.99656245383913</v>
+        <v>-27.82036967812391</v>
       </c>
       <c r="F39">
-        <v>-1.341238801979285</v>
+        <v>-1.701755064453867</v>
       </c>
       <c r="G39">
-        <v>-3.77777099267396</v>
+        <v>-6.218038434983911</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.288046559373616</v>
       </c>
       <c r="E40">
-        <v>-23.70907228146217</v>
+        <v>-28.34409675405901</v>
       </c>
       <c r="F40">
-        <v>-1.535008019739937</v>
+        <v>-1.403112048396589</v>
       </c>
       <c r="G40">
-        <v>-3.999588132535542</v>
+        <v>-6.641381640583468</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.856173416100294</v>
       </c>
       <c r="E41">
-        <v>-23.78030064912882</v>
+        <v>-26.70909574206363</v>
       </c>
       <c r="F41">
-        <v>-1.44972511051952</v>
+        <v>-1.551017876533843</v>
       </c>
       <c r="G41">
-        <v>-3.076550976869708</v>
+        <v>-6.641824605493993</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.474250540673092</v>
       </c>
       <c r="E42">
-        <v>-23.56714084911377</v>
+        <v>-28.00115994593214</v>
       </c>
       <c r="F42">
-        <v>-1.918271251095393</v>
+        <v>-1.669897710877003</v>
       </c>
       <c r="G42">
-        <v>-3.650249597987701</v>
+        <v>-6.756765796721342</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.148116113761965</v>
       </c>
       <c r="E43">
-        <v>-23.03577423752774</v>
+        <v>-26.175605276168</v>
       </c>
       <c r="F43">
-        <v>-1.819559677908193</v>
+        <v>-1.5274516522916</v>
       </c>
       <c r="G43">
-        <v>-2.788564723040365</v>
+        <v>-6.359665801154224</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.887036554238547</v>
       </c>
       <c r="E44">
-        <v>-22.83863165007782</v>
+        <v>-28.3794007374228</v>
       </c>
       <c r="F44">
-        <v>-1.862861755522134</v>
+        <v>-1.342015810603111</v>
       </c>
       <c r="G44">
-        <v>-2.42630473799143</v>
+        <v>-5.946560006820134</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.691836392907984</v>
       </c>
       <c r="E45">
-        <v>-21.78132806724095</v>
+        <v>-26.41396150556173</v>
       </c>
       <c r="F45">
-        <v>-1.710939173848705</v>
+        <v>-1.687882395559183</v>
       </c>
       <c r="G45">
-        <v>-3.015287289133316</v>
+        <v>-5.779286612941202</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.561283008305521</v>
       </c>
       <c r="E46">
-        <v>-22.34385057999975</v>
+        <v>-26.50850245741987</v>
       </c>
       <c r="F46">
-        <v>-1.883370475680644</v>
+        <v>-1.708987540247709</v>
       </c>
       <c r="G46">
-        <v>-2.324481870558742</v>
+        <v>-5.942530666745136</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.493524317901674</v>
       </c>
       <c r="E47">
-        <v>-21.91820119412278</v>
+        <v>-26.96420279681173</v>
       </c>
       <c r="F47">
-        <v>-2.077245724468854</v>
+        <v>-2.066477776599863</v>
       </c>
       <c r="G47">
-        <v>-2.185400732318558</v>
+        <v>-6.229384899136471</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.481910655558281</v>
       </c>
       <c r="E48">
-        <v>-21.25832101867308</v>
+        <v>-25.29595372865204</v>
       </c>
       <c r="F48">
-        <v>-2.210332888137429</v>
+        <v>-2.147667722483049</v>
       </c>
       <c r="G48">
-        <v>-2.688520277692895</v>
+        <v>-6.503284868811119</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.523379479656197</v>
       </c>
       <c r="E49">
-        <v>-21.4487931639097</v>
+        <v>-24.70027825768308</v>
       </c>
       <c r="F49">
-        <v>-2.058433500751278</v>
+        <v>-1.979722858504671</v>
       </c>
       <c r="G49">
-        <v>-2.039724338743891</v>
+        <v>-5.980477994080114</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.608229329605328</v>
       </c>
       <c r="E50">
-        <v>-20.42095636144074</v>
+        <v>-24.41213598504903</v>
       </c>
       <c r="F50">
-        <v>-2.215148187849902</v>
+        <v>-1.690687247585062</v>
       </c>
       <c r="G50">
-        <v>-2.107652187467516</v>
+        <v>-6.822577257539124</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.732267924921918</v>
       </c>
       <c r="E51">
-        <v>-20.39744905286693</v>
+        <v>-23.81975271468364</v>
       </c>
       <c r="F51">
-        <v>-2.131229599741896</v>
+        <v>-1.608591067763214</v>
       </c>
       <c r="G51">
-        <v>-2.385663527756148</v>
+        <v>-6.391756148005593</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.88566563186249</v>
       </c>
       <c r="E52">
-        <v>-20.10272690749972</v>
+        <v>-24.95133232819432</v>
       </c>
       <c r="F52">
-        <v>-2.247767639437341</v>
+        <v>-1.838911997172395</v>
       </c>
       <c r="G52">
-        <v>-2.888563231286001</v>
+        <v>-6.136979137579389</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.062888086684697</v>
       </c>
       <c r="E53">
-        <v>-18.95562821356476</v>
+        <v>-24.15904862970834</v>
       </c>
       <c r="F53">
-        <v>-2.38274099568209</v>
+        <v>-1.452631851735943</v>
       </c>
       <c r="G53">
-        <v>-2.506757009407455</v>
+        <v>-6.016305652287691</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.256306218615832</v>
       </c>
       <c r="E54">
-        <v>-19.00434100846527</v>
+        <v>-23.05703995146776</v>
       </c>
       <c r="F54">
-        <v>-2.443888592254541</v>
+        <v>-2.11759301555701</v>
       </c>
       <c r="G54">
-        <v>-3.170646567529904</v>
+        <v>-7.02729595185444</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.459460935991139</v>
       </c>
       <c r="E55">
-        <v>-19.39397091208523</v>
+        <v>-23.75276299868818</v>
       </c>
       <c r="F55">
-        <v>-2.275385408646676</v>
+        <v>-2.015403127645455</v>
       </c>
       <c r="G55">
-        <v>-2.860108477922497</v>
+        <v>-5.947547654509527</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.666699034575472</v>
       </c>
       <c r="E56">
-        <v>-18.136314053727</v>
+        <v>-22.37506987980863</v>
       </c>
       <c r="F56">
-        <v>-2.416558266533977</v>
+        <v>-2.165795714725913</v>
       </c>
       <c r="G56">
-        <v>-2.978179954517556</v>
+        <v>-5.577573517574337</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.868783587062361</v>
       </c>
       <c r="E57">
-        <v>-18.58690627443822</v>
+        <v>-21.75576483146765</v>
       </c>
       <c r="F57">
-        <v>-2.585157540760566</v>
+        <v>-2.182204016240566</v>
       </c>
       <c r="G57">
-        <v>-2.889357286903387</v>
+        <v>-6.64072211505002</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.061524887547759</v>
       </c>
       <c r="E58">
-        <v>-17.66423422384939</v>
+        <v>-22.13532340889455</v>
       </c>
       <c r="F58">
-        <v>-2.462551709839614</v>
+        <v>-2.257917625223843</v>
       </c>
       <c r="G58">
-        <v>-3.345827705367098</v>
+        <v>-7.309763191020798</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.235412596317499</v>
       </c>
       <c r="E59">
-        <v>-17.48194050267062</v>
+        <v>-21.75126805677803</v>
       </c>
       <c r="F59">
-        <v>-2.3535982020842</v>
+        <v>-1.825824620575565</v>
       </c>
       <c r="G59">
-        <v>-3.750458104413142</v>
+        <v>-6.838484619659313</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.385099258536275</v>
       </c>
       <c r="E60">
-        <v>-18.16651444688415</v>
+        <v>-22.70975580829353</v>
       </c>
       <c r="F60">
-        <v>-2.674486196376256</v>
+        <v>-2.259921445971215</v>
       </c>
       <c r="G60">
-        <v>-3.618799089340423</v>
+        <v>-7.436582404293336</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.504184709893797</v>
       </c>
       <c r="E61">
-        <v>-17.36022417829246</v>
+        <v>-22.43768056143868</v>
       </c>
       <c r="F61">
-        <v>-2.393864313166882</v>
+        <v>-1.928325146263171</v>
       </c>
       <c r="G61">
-        <v>-4.274022941324379</v>
+        <v>-7.395206200428738</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.586937479288022</v>
       </c>
       <c r="E62">
-        <v>-17.38604100861018</v>
+        <v>-22.04860766012167</v>
       </c>
       <c r="F62">
-        <v>-2.661318468141355</v>
+        <v>-2.201348415286665</v>
       </c>
       <c r="G62">
-        <v>-4.493884473136531</v>
+        <v>-7.17520357608953</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.63076703131483</v>
       </c>
       <c r="E63">
-        <v>-17.28311785136385</v>
+        <v>-21.03342341403014</v>
       </c>
       <c r="F63">
-        <v>-2.61260052444791</v>
+        <v>-2.378128645983302</v>
       </c>
       <c r="G63">
-        <v>-5.081410161906024</v>
+        <v>-8.098056983348034</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.630163423969804</v>
       </c>
       <c r="E64">
-        <v>-16.65958773677371</v>
+        <v>-21.06414005322417</v>
       </c>
       <c r="F64">
-        <v>-2.735699233973528</v>
+        <v>-1.812535122332453</v>
       </c>
       <c r="G64">
-        <v>-5.254599598256635</v>
+        <v>-8.426658197640185</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.586492580587133</v>
       </c>
       <c r="E65">
-        <v>-17.31814106933917</v>
+        <v>-20.0200007443276</v>
       </c>
       <c r="F65">
-        <v>-2.821837846721038</v>
+        <v>-2.341740122713125</v>
       </c>
       <c r="G65">
-        <v>-5.049096691988613</v>
+        <v>-8.527680447012369</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.500181159147385</v>
       </c>
       <c r="E66">
-        <v>-16.86473213779519</v>
+        <v>-20.97951193096883</v>
       </c>
       <c r="F66">
-        <v>-3.123955035665657</v>
+        <v>-2.545154022144572</v>
       </c>
       <c r="G66">
-        <v>-4.905608873194095</v>
+        <v>-8.636508722474471</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.375031845634152</v>
       </c>
       <c r="E67">
-        <v>-15.66436047563399</v>
+        <v>-20.64545998884501</v>
       </c>
       <c r="F67">
-        <v>-2.914878416668672</v>
+        <v>-2.614394768242374</v>
       </c>
       <c r="G67">
-        <v>-5.164461160797129</v>
+        <v>-9.526878036294473</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.219162524891855</v>
       </c>
       <c r="E68">
-        <v>-16.37942463534117</v>
+        <v>-20.34309830782686</v>
       </c>
       <c r="F68">
-        <v>-3.002198281332574</v>
+        <v>-2.227661505836592</v>
       </c>
       <c r="G68">
-        <v>-5.859007171949471</v>
+        <v>-8.154700711128728</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.039406409651384</v>
       </c>
       <c r="E69">
-        <v>-16.4870075923414</v>
+        <v>-20.81630119925838</v>
       </c>
       <c r="F69">
-        <v>-3.034184031856871</v>
+        <v>-2.293030462693709</v>
       </c>
       <c r="G69">
-        <v>-6.125931264588739</v>
+        <v>-9.516171410346004</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.849649411766495</v>
       </c>
       <c r="E70">
-        <v>-15.91188686489325</v>
+        <v>-20.06149968013389</v>
       </c>
       <c r="F70">
-        <v>-3.177969560532601</v>
+        <v>-3.208781514447132</v>
       </c>
       <c r="G70">
-        <v>-5.273253342822078</v>
+        <v>-8.994936240741975</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.659284784671629</v>
       </c>
       <c r="E71">
-        <v>-16.62691479680837</v>
+        <v>-19.77930782234591</v>
       </c>
       <c r="F71">
-        <v>-3.41066624765301</v>
+        <v>-2.527242233793838</v>
       </c>
       <c r="G71">
-        <v>-6.284217392616352</v>
+        <v>-8.606528201085824</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.481056601515969</v>
       </c>
       <c r="E72">
-        <v>-16.69524946958412</v>
+        <v>-18.81623272666065</v>
       </c>
       <c r="F72">
-        <v>-3.354401048552659</v>
+        <v>-2.569749907068495</v>
       </c>
       <c r="G72">
-        <v>-5.824045756233587</v>
+        <v>-10.32885452252459</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.322998280191793</v>
       </c>
       <c r="E73">
-        <v>-16.89848738304836</v>
+        <v>-20.14072986137209</v>
       </c>
       <c r="F73">
-        <v>-3.258493499023936</v>
+        <v>-3.209947855750273</v>
       </c>
       <c r="G73">
-        <v>-5.813056945231007</v>
+        <v>-9.563063347652029</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.191136290410745</v>
       </c>
       <c r="E74">
-        <v>-16.71390678249572</v>
+        <v>-20.91996249776796</v>
       </c>
       <c r="F74">
-        <v>-3.45863120537731</v>
+        <v>-2.744718498255209</v>
       </c>
       <c r="G74">
-        <v>-5.683031978494891</v>
+        <v>-8.554596307464493</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.092476401218939</v>
       </c>
       <c r="E75">
-        <v>-16.68556759215572</v>
+        <v>-20.77616080565439</v>
       </c>
       <c r="F75">
-        <v>-3.897950887247611</v>
+        <v>-2.592208604093195</v>
       </c>
       <c r="G75">
-        <v>-6.007167450244637</v>
+        <v>-8.710533080855544</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.02733512472412</v>
       </c>
       <c r="E76">
-        <v>-17.06038032882258</v>
+        <v>-19.4097209446839</v>
       </c>
       <c r="F76">
-        <v>-3.885858379901544</v>
+        <v>-3.255192454923779</v>
       </c>
       <c r="G76">
-        <v>-5.084750445453539</v>
+        <v>-8.997042784983138</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.999590359143267</v>
       </c>
       <c r="E77">
-        <v>-17.68840721810233</v>
+        <v>-21.69825321157024</v>
       </c>
       <c r="F77">
-        <v>-3.722765263801363</v>
+        <v>-3.164800175562895</v>
       </c>
       <c r="G77">
-        <v>-5.335245461744667</v>
+        <v>-8.58682446562136</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.00609936927207</v>
       </c>
       <c r="E78">
-        <v>-17.57971025649622</v>
+        <v>-20.73323992900969</v>
       </c>
       <c r="F78">
-        <v>-3.890034179979056</v>
+        <v>-3.77850859143795</v>
       </c>
       <c r="G78">
-        <v>-5.372782636384715</v>
+        <v>-9.751710618769184</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.048497172119967</v>
       </c>
       <c r="E79">
-        <v>-18.13449813564992</v>
+        <v>-21.88939104248599</v>
       </c>
       <c r="F79">
-        <v>-3.906805306416135</v>
+        <v>-3.236795243275005</v>
       </c>
       <c r="G79">
-        <v>-5.170455952586234</v>
+        <v>-8.627629736934614</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.123366071947518</v>
       </c>
       <c r="E80">
-        <v>-18.3883508030979</v>
+        <v>-22.69443598072558</v>
       </c>
       <c r="F80">
-        <v>-4.004764722001593</v>
+        <v>-3.608828297750708</v>
       </c>
       <c r="G80">
-        <v>-4.035606101593566</v>
+        <v>-8.295402772819276</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.23076592547566</v>
       </c>
       <c r="E81">
-        <v>-19.58578348562812</v>
+        <v>-21.95367725949887</v>
       </c>
       <c r="F81">
-        <v>-4.138584990821645</v>
+        <v>-3.487471644873178</v>
       </c>
       <c r="G81">
-        <v>-4.898216281020666</v>
+        <v>-8.269005345373545</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.370344928849517</v>
       </c>
       <c r="E82">
-        <v>-20.26495948882451</v>
+        <v>-23.90077617162888</v>
       </c>
       <c r="F82">
-        <v>-4.077689217939645</v>
+        <v>-4.038125562414538</v>
       </c>
       <c r="G82">
-        <v>-4.721158284451469</v>
+        <v>-9.092437739380873</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.539493831236705</v>
       </c>
       <c r="E83">
-        <v>-19.72879269479035</v>
+        <v>-24.05378877987405</v>
       </c>
       <c r="F83">
-        <v>-4.210752358953538</v>
+        <v>-4.032756084909591</v>
       </c>
       <c r="G83">
-        <v>-4.446296916859905</v>
+        <v>-7.528945509970145</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.739791325975417</v>
       </c>
       <c r="E84">
-        <v>-21.77375645870012</v>
+        <v>-24.57870231599916</v>
       </c>
       <c r="F84">
-        <v>-4.218845508478889</v>
+        <v>-3.658194024753142</v>
       </c>
       <c r="G84">
-        <v>-4.454631219620894</v>
+        <v>-8.338209589283792</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.965942194807231</v>
       </c>
       <c r="E85">
-        <v>-22.62238795926354</v>
+        <v>-25.36680623297605</v>
       </c>
       <c r="F85">
-        <v>-4.129818378597818</v>
+        <v>-3.586888987087563</v>
       </c>
       <c r="G85">
-        <v>-4.6434523954807</v>
+        <v>-7.688859123891243</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.220145452744891</v>
       </c>
       <c r="E86">
-        <v>-23.45243007402547</v>
+        <v>-26.8442163495045</v>
       </c>
       <c r="F86">
-        <v>-4.285523285832429</v>
+        <v>-3.635751066709095</v>
       </c>
       <c r="G86">
-        <v>-4.840000848112997</v>
+        <v>-8.271636885064218</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.494643802208675</v>
       </c>
       <c r="E87">
-        <v>-24.58037332290799</v>
+        <v>-27.77746238690124</v>
       </c>
       <c r="F87">
-        <v>-4.260683032524681</v>
+        <v>-3.5739101266205</v>
       </c>
       <c r="G87">
-        <v>-4.113095429941413</v>
+        <v>-7.482161852975582</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.789763102596329</v>
       </c>
       <c r="E88">
-        <v>-25.96751736704154</v>
+        <v>-28.2094289940189</v>
       </c>
       <c r="F88">
-        <v>-4.293097877363628</v>
+        <v>-3.916866656890538</v>
       </c>
       <c r="G88">
-        <v>-4.325767805316822</v>
+        <v>-7.269601039133194</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.101517063949815</v>
       </c>
       <c r="E89">
-        <v>-27.37221377642883</v>
+        <v>-30.37096700007113</v>
       </c>
       <c r="F89">
-        <v>-4.355495480346904</v>
+        <v>-3.475997927977001</v>
       </c>
       <c r="G89">
-        <v>-4.967643647996956</v>
+        <v>-7.510511607249184</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.425844290902476</v>
       </c>
       <c r="E90">
-        <v>-27.89978552679643</v>
+        <v>-32.04509855596679</v>
       </c>
       <c r="F90">
-        <v>-4.655636184668444</v>
+        <v>-4.355069699501865</v>
       </c>
       <c r="G90">
-        <v>-4.694600077149325</v>
+        <v>-7.871508321997733</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.764448989657188</v>
       </c>
       <c r="E91">
-        <v>-30.16576146465055</v>
+        <v>-33.73907614920105</v>
       </c>
       <c r="F91">
-        <v>-4.356760397370978</v>
+        <v>-4.266020203700919</v>
       </c>
       <c r="G91">
-        <v>-4.997332140666813</v>
+        <v>-8.233207218160002</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.110798386577796</v>
       </c>
       <c r="E92">
-        <v>-31.56845628852644</v>
+        <v>-34.71453435706029</v>
       </c>
       <c r="F92">
-        <v>-4.41500539456402</v>
+        <v>-3.595059174781375</v>
       </c>
       <c r="G92">
-        <v>-4.60858613519004</v>
+        <v>-7.330365981192551</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.469713280997773</v>
       </c>
       <c r="E93">
-        <v>-33.0219583265314</v>
+        <v>-34.90063652487952</v>
       </c>
       <c r="F93">
-        <v>-4.557264242116391</v>
+        <v>-4.404360045070644</v>
       </c>
       <c r="G93">
-        <v>-5.033527295689047</v>
+        <v>-7.10145484031945</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.833123762405181</v>
       </c>
       <c r="E94">
-        <v>-35.70805438349912</v>
+        <v>-37.6737924946447</v>
       </c>
       <c r="F94">
-        <v>-4.284467945761263</v>
+        <v>-4.346317997891288</v>
       </c>
       <c r="G94">
-        <v>-5.034603536360545</v>
+        <v>-7.641639064429274</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.203346333877947</v>
       </c>
       <c r="E95">
-        <v>-36.92556179130534</v>
+        <v>-38.54106545846069</v>
       </c>
       <c r="F95">
-        <v>-4.327569558463727</v>
+        <v>-3.782366298432787</v>
       </c>
       <c r="G95">
-        <v>-5.058444892211471</v>
+        <v>-8.36647075057529</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.582061101230474</v>
       </c>
       <c r="E96">
-        <v>-39.365424338343</v>
+        <v>-40.92206916458365</v>
       </c>
       <c r="F96">
-        <v>-4.24385806220642</v>
+        <v>-4.493015237987859</v>
       </c>
       <c r="G96">
-        <v>-6.066800370865986</v>
+        <v>-8.475397462684176</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.960910432024798</v>
       </c>
       <c r="E97">
-        <v>-42.22097136420374</v>
+        <v>-44.01161829207975</v>
       </c>
       <c r="F97">
-        <v>-4.363618451098755</v>
+        <v>-3.811467673660537</v>
       </c>
       <c r="G97">
-        <v>-5.808207299766147</v>
+        <v>-8.648491743609563</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.35466855098074</v>
       </c>
       <c r="E98">
-        <v>-43.792729972445</v>
+        <v>-45.56760422535229</v>
       </c>
       <c r="F98">
-        <v>-4.156968948591975</v>
+        <v>-3.91261216190976</v>
       </c>
       <c r="G98">
-        <v>-6.909660877726787</v>
+        <v>-8.372281793957066</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.74357249455488</v>
       </c>
       <c r="E99">
-        <v>-45.65826427498585</v>
+        <v>-45.23081255645383</v>
       </c>
       <c r="F99">
-        <v>-4.262777973686361</v>
+        <v>-4.287748280676349</v>
       </c>
       <c r="G99">
-        <v>-6.590873797118936</v>
+        <v>-8.53062698397275</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.15800634120399</v>
       </c>
       <c r="E100">
-        <v>-47.66462732645424</v>
+        <v>-47.26215919902254</v>
       </c>
       <c r="F100">
-        <v>-4.125517495042483</v>
+        <v>-4.262781287155972</v>
       </c>
       <c r="G100">
-        <v>-7.41097247002187</v>
+        <v>-9.123015443093339</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.55660678095754</v>
       </c>
       <c r="E101">
-        <v>-49.6134685689587</v>
+        <v>-50.80464063617332</v>
       </c>
       <c r="F101">
-        <v>-4.241319944484243</v>
+        <v>-4.032232556711022</v>
       </c>
       <c r="G101">
-        <v>-7.159132152891369</v>
+        <v>-9.719406992516451</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.00757007003444</v>
       </c>
       <c r="E102">
-        <v>-51.58268794449768</v>
+        <v>-52.47552640832397</v>
       </c>
       <c r="F102">
-        <v>-3.897697406822354</v>
+        <v>-4.71516100949881</v>
       </c>
       <c r="G102">
-        <v>-7.960435988701803</v>
+        <v>-9.942543183444929</v>
       </c>
     </row>
   </sheetData>
